--- a/10. Equity/work/fundamentals_model/20260721_ファンダメンタルズの検討③/data/input/factor_master.xlsx
+++ b/10. Equity/work/fundamentals_model/20260721_ファンダメンタルズの検討③/data/input/factor_master.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R38cdabadce184951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Dictionary" sheetId="2" r:id="Rc50c96e4bcb5423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Option_Dictionary" sheetId="3" r:id="R2afc8c079c1448cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor_Master" sheetId="4" r:id="R98132a8167d84723"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Settings" sheetId="5" r:id="R81a8815c7313409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Engineering_Control" sheetId="6" r:id="R44578045d82b4cdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derived_Feature_Rules" sheetId="7" r:id="R7cda7b0cba234bb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor_Overrides" sheetId="8" r:id="R1b1550666a5748ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Overrides" sheetId="9" r:id="R7b2b8a661f5f49da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country_Region_Map" sheetId="10" r:id="R799e3ba1017449ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector_Group_Map" sheetId="11" r:id="Re3b2fd31407a4003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector_Factor_Interaction" sheetId="12" r:id="R0ab79230ad3c4dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer3_Settings" sheetId="13" r:id="R32b6340793724817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rbbb58dfdf8874027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Dictionary" sheetId="2" r:id="Rb57398858fb14bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Option_Dictionary" sheetId="3" r:id="R7d004060908d46ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor_Master" sheetId="4" r:id="R58171fb6e5934a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Settings" sheetId="5" r:id="R4ccd305d513a4f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Engineering_Control" sheetId="6" r:id="R5362ddbd113b498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derived_Feature_Rules" sheetId="7" r:id="R7256139407fa452f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor_Overrides" sheetId="8" r:id="R18e155b94e6541bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Overrides" sheetId="9" r:id="R278940024a664fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country_Region_Map" sheetId="10" r:id="Rb0dae83ca1f34f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector_Group_Map" sheetId="11" r:id="Rbfc3d64db0e94d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector_Factor_Interaction" sheetId="12" r:id="Ra3006397815d40be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer3_Settings" sheetId="13" r:id="R165b29eabf474b6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,7 +57,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,6 +87,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF44546A"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -261,7 +276,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="114">
+  <x:cellXfs count="127">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -552,6 +567,35 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1220,6 +1264,90 @@
       <x:c r="C43" s="27"/>
       <x:c r="D43" s="27"/>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="126" t="str">
+        <x:v>v0.12.2評価変更</x:v>
+      </x:c>
+      <x:c r="B45" s="126" t="str">
+        <x:v>内容</x:v>
+      </x:c>
+      <x:c r="C45" s="126" t="str">
+        <x:v>初期設定</x:v>
+      </x:c>
+      <x:c r="D45" s="126" t="str">
+        <x:v>注意</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="27" t="str">
+        <x:v>共通OOS</x:v>
+      </x:c>
+      <x:c r="B46" s="27" t="str">
+        <x:v>全シナリオでDate×ISINが共通する銘柄集合に再限定し、順位と分位を再計算</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="str">
+        <x:v>主比較</x:v>
+      </x:c>
+      <x:c r="D46" s="27" t="str">
+        <x:v>各モデル利用可能期間は補助評価</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="27" t="str">
+        <x:v>2018年開始への対応</x:v>
+      </x:c>
+      <x:c r="B47" s="27" t="str">
+        <x:v>Layer1最低18か月、Layer3はLayer2 OOF蓄積後12か月で初回予測</x:v>
+      </x:c>
+      <x:c r="C47" s="27" t="str">
+        <x:v>Lookback=36</x:v>
+      </x:c>
+      <x:c r="D47" s="27" t="str">
+        <x:v>短期化しすぎると推定不安定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="27" t="str">
+        <x:v>S07 OLS</x:v>
+      </x:c>
+      <x:c r="B48" s="27" t="str">
+        <x:v>線形基底のみ・無正則化OLS</x:v>
+      </x:c>
+      <x:c r="C48" s="27" t="str">
+        <x:v>Enabled=1</x:v>
+      </x:c>
+      <x:c r="D48" s="27" t="str">
+        <x:v>係数安定性を確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="27" t="str">
+        <x:v>S07 Ridge</x:v>
+      </x:c>
+      <x:c r="B49" s="27" t="str">
+        <x:v>OLSと同じ線形基底・Ridge</x:v>
+      </x:c>
+      <x:c r="C49" s="27" t="str">
+        <x:v>Enabled=1</x:v>
+      </x:c>
+      <x:c r="D49" s="27" t="str">
+        <x:v>OLSとの差が正則化効果</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="27" t="str">
+        <x:v>S07 Flexible</x:v>
+      </x:c>
+      <x:c r="B50" s="27" t="str">
+        <x:v>3基底Ridge</x:v>
+      </x:c>
+      <x:c r="C50" s="27" t="str">
+        <x:v>Enabled=0</x:v>
+      </x:c>
+      <x:c r="D50" s="27" t="str">
+        <x:v>補助比較として必要時のみ有効化</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
@@ -1570,63 +1698,111 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="115" t="str">
         <x:v>Setting</x:v>
       </x:c>
-      <x:c r="B1" s="44" t="str">
+      <x:c r="B1" s="116" t="str">
         <x:v>Value</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
-      <x:c r="A2" s="86" t="str">
+      <x:c r="A2" s="117" t="str">
         <x:v>Estimation_Scope</x:v>
       </x:c>
-      <x:c r="B2" s="88" t="str">
+      <x:c r="B2" s="118" t="str">
         <x:v>country_independent</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
-      <x:c r="A3" s="86" t="str">
+      <x:c r="A3" s="117" t="str">
         <x:v>Training_Mode</x:v>
       </x:c>
-      <x:c r="B3" s="88" t="str">
+      <x:c r="B3" s="118" t="str">
         <x:v>rolling_pooled</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
-      <x:c r="A4" s="86" t="str">
+      <x:c r="A4" s="117" t="str">
         <x:v>Interaction_Mode</x:v>
       </x:c>
-      <x:c r="B4" s="88" t="str">
+      <x:c r="B4" s="118" t="str">
         <x:v>selected_interactions</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
-      <x:c r="A5" s="86" t="str">
+      <x:c r="A5" s="117" t="str">
         <x:v>Include_Nonlinear_Basis</x:v>
       </x:c>
-      <x:c r="B5" s="88" t="n">
+      <x:c r="B5" s="118" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
-      <x:c r="A6" s="86" t="str">
+      <x:c r="A6" s="117" t="str">
         <x:v>Include_Sector_Dummy</x:v>
       </x:c>
-      <x:c r="B6" s="88" t="n">
+      <x:c r="B6" s="118" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
-      <x:c r="A7" s="89" t="str">
+      <x:c r="A7" s="119" t="str">
         <x:v>Include_Sector_Factor_Interaction</x:v>
       </x:c>
-      <x:c r="B7" s="91" t="n">
+      <x:c r="B7" s="120" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="122" t="str">
+        <x:v>Lookback_Periods</x:v>
+      </x:c>
+      <x:c r="B8" s="122" t="n">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="122" t="str">
+        <x:v>Minimum_Train_Periods</x:v>
+      </x:c>
+      <x:c r="B9" s="122" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="122" t="str">
+        <x:v>Ridge_Validation_Periods</x:v>
+      </x:c>
+      <x:c r="B10" s="122" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="122" t="str">
+        <x:v>S07_OLS_Linear_Enabled</x:v>
+      </x:c>
+      <x:c r="B11" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="122" t="str">
+        <x:v>S07_Ridge_Linear_Enabled</x:v>
+      </x:c>
+      <x:c r="B12" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="122" t="str">
+        <x:v>S07_Ridge_Flexible_Enabled</x:v>
+      </x:c>
+      <x:c r="B13" s="122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="6">
+  <x:dataValidations count="9">
     <x:dataValidation type="list" sqref="B2">
       <x:formula1>"country_independent,regional_pooling,hierarchical_partial_pooling"</x:formula1>
     </x:dataValidation>
@@ -1643,6 +1819,15 @@
       <x:formula1>"0,1"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="B7">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="B11">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="B12">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="B13">
       <x:formula1>"0,1"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -3144,6 +3329,180 @@
         <x:v>選択肢以外</x:v>
       </x:c>
     </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>Layer3_Settings</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>Lookback_Periods</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>12以上</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>空欄はPython Config</x:v>
+      </x:c>
+      <x:c r="G52" t="str">
+        <x:v>第3層が各予測時点で参照する最大過去月数。2018年開始データでは36を初期値とする。</x:v>
+      </x:c>
+      <x:c r="H52" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>データ履歴より長い値を設定しても初期OOSが増えるわけではない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>Layer3_Settings</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>Minimum_Train_Periods</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>6以上かつLookback以下</x:v>
+      </x:c>
+      <x:c r="F53" t="str">
+        <x:v>空欄はPython Config</x:v>
+      </x:c>
+      <x:c r="G53" t="str">
+        <x:v>Layer1のOOF FactorScoreが利用可能になった後、第3層の初回OOS予測に必要な最低月数。</x:v>
+      </x:c>
+      <x:c r="H53" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>2018年開始データで大きくしすぎ、共通OOS期間が極端に短くなる</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>Layer3_Settings</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>Ridge_Validation_Periods</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>3以上</x:v>
+      </x:c>
+      <x:c r="F54" t="str">
+        <x:v>空欄はPython Config</x:v>
+      </x:c>
+      <x:c r="G54" t="str">
+        <x:v>Ridgeのalphaを選択するために、各学習窓の末尾から使用する検証月数。最終係数は学習+検証で再推定する。</x:v>
+      </x:c>
+      <x:c r="H54" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>Minimum_Train_Periods以上を設定する</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>Layer3_Settings</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>S07_OLS_Linear_Enabled</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>空欄はPython Config</x:v>
+      </x:c>
+      <x:c r="G55" t="str">
+        <x:v>1なら、線形基底のみ・無正則化OLSのS07を生成する。</x:v>
+      </x:c>
+      <x:c r="H55" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>Ridgeとの比較時に0にしてしまう</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>Layer3_Settings</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>S07_Ridge_Linear_Enabled</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>空欄はPython Config</x:v>
+      </x:c>
+      <x:c r="G56" t="str">
+        <x:v>1なら、OLSと同じ線形基底にRidge正則化を加えたS07を生成する。</x:v>
+      </x:c>
+      <x:c r="H56" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>OLSと異なる基底を使い、正則化効果を分離できなくなる</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>Layer3_Settings</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>S07_Ridge_Flexible_Enabled</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D57" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F57" t="str">
+        <x:v>空欄はPython Config</x:v>
+      </x:c>
+      <x:c r="G57" t="str">
+        <x:v>1なら、線形・区分線形・二次基底を同時投入するRidgeを補助比較として生成する。</x:v>
+      </x:c>
+      <x:c r="H57" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>初期分析で有効化し、説明変数数と過学習リスクを急増させる</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3959,6 +4318,86 @@
       </x:c>
       <x:c r="F40" s="63" t="str">
         <x:v>all_interactions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>S07 Estimator</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>ols</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>無正則化の最小二乗法</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Ridgeの追加価値を確認する基準</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>多重共線性で係数が不安定になり得る</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>S07_OLS_Linear</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>S07 Estimator</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>ridge</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>L2正則化付き線形回帰</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>交差項や相関するFactorScoreの安定化</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>alpha選択は過去検証期間だけで行う</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>S07_Ridge_Linear</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>S07 Basis</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>linear</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>FactorScoreの線形項のみ</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>OLS/Ridgeの公平な比較・初期本線</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>非線形性は第1層で既に反映されている</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>linear</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>S07 Basis</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>linear,piecewise,quadratic</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>3基底を同時投入</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>非線形性の補助比較</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>特徴量数と説明負荷が増える</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>S07_Ridge_Flexible</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
